--- a/docs/WBS_모델하우스_컨피규레이터.xlsx
+++ b/docs/WBS_모델하우스_컨피규레이터.xlsx
@@ -214,7 +214,7 @@
   </si>
   <si>
     <t>FR-01,NFR-03
-1unit=1m, scale1, 문1.9~2.2m, 벽 관통 방지</t>
+1unit=1m, scale1, 문 높이 에셋 기본(약 2.5m), 벽 관통 방지</t>
   </si>
   <si>
     <t>2.05 4개 구역·입구·거실주방 경계 배치</t>
@@ -308,11 +308,11 @@
 입실1초, 퇴실3초 대기+1초 감광</t>
   </si>
   <si>
-    <t>3.06 중문 양방향 자동 개폐 구현</t>
-  </si>
-  <si>
-    <t>FR-07
-1.5m 감지, 열기1초, 이탈3초 후1초 닫기</t>
+    <t>3.06 (삭제) 중문 자동 개폐</t>
+  </si>
+  <si>
+    <t>FR-07 삭제
+10/9 팀 결정으로 중문 제외(SRS v2.5), 작업 없음</t>
   </si>
   <si>
     <t>3.07 구역 정보 팝업 구현</t>
@@ -483,25 +483,25 @@
 최신 기록 위쪽, 패널 중 이동·타이머 계속</t>
   </si>
   <si>
-    <t>4.14 중복 주문·컵 없음·실패 복귀 처리</t>
+    <t>4.14 커피 중 재클릭 무시·실패 복귀 처리</t>
   </si>
   <si>
     <t>FR-13/15
-작업 중 주문 무시, 컵 없음 안내, 실패 후 홈</t>
-  </si>
-  <si>
-    <t>4.15 월드 UI·빌보드·거리 제어</t>
-  </si>
-  <si>
-    <t>FR-34
-5m 이내 클릭,0.5초 열림, 멀어지면 숨김</t>
-  </si>
-  <si>
-    <t>4.16 버튼 활성·작업명·수동 미구현 표시</t>
-  </si>
-  <si>
-    <t>FR-34
-커피 작업·컵 유무로 제어, 수동 미채택 시 비활성 안내</t>
+커피 중·완료 3초 이내 클릭 무시, 실패 후 홈</t>
+  </si>
+  <si>
+    <t>4.15 커피 로봇팔 클릭 시연 흐름</t>
+  </si>
+  <si>
+    <t>FR-13/TC-16
+5m 이내 클릭·테두리, 컵 든 채 5초 추출, 식탁에 놓기, 30초 이내</t>
+  </si>
+  <si>
+    <t>4.16 커피 시연 반복·기록 확인</t>
+  </si>
+  <si>
+    <t>FR-13/25/TC-33
+완료 3초 뒤 빈 컵 복귀 후 재클릭 반복, 시작·상태·완료 기록 순서</t>
   </si>
   <si>
     <t>4.17 작업·타이머 취소 및 상태 복구</t>
@@ -532,18 +532,18 @@
 아일랜드3곳·머신 통과, 도달 불가 실패 처리</t>
   </si>
   <si>
-    <t>4.21 퇴실·재진입·문 재접근 경계 시험</t>
-  </si>
-  <si>
-    <t>FR-04/05/07
-2초·3.5초 재진입 및 문 닫힘 취소 검증</t>
+    <t>4.21 퇴실·재진입 경계 시험</t>
+  </si>
+  <si>
+    <t>FR-04/05
+2초·3.5초 재진입 검증</t>
   </si>
   <si>
     <t>4.22 필수 기능 전체 시나리오 점검</t>
   </si>
   <si>
     <t>Must 전체
-Must15개 실행 증거 확보, 실패 항목 등록</t>
+Must 13개 실행 증거 확보, 실패 항목 등록</t>
   </si>
   <si>
     <t>4.23 이벤트·커피·비용 통합 결함 수정</t>
@@ -744,53 +744,53 @@
     <t>선택·확장 (미배정)</t>
   </si>
   <si>
-    <t>7.01 최초 현관 웰컴 음성·자막</t>
-  </si>
-  <si>
-    <t>FR-08
-최초1회, 음원 없음은 자막·로그, 리셋 후 재허용</t>
-  </si>
-  <si>
-    <t>7.02 온도24도·로봇 상태 안내</t>
-  </si>
-  <si>
-    <t>FR-10
-웰컴 뒤 실제 로봇 상태 안내, 음원 대체 경로</t>
-  </si>
-  <si>
-    <t>7.03 수동 모드·XYZ 이동·범위 제한</t>
-  </si>
-  <si>
-    <t>FR-33
-10cm/s, 도달 불가 제한, 종료 시 홈·idle</t>
-  </si>
-  <si>
-    <t>7.04 수동 버튼·그립·해제 연결</t>
-  </si>
-  <si>
-    <t>FR-33/34
-5cm 내 집기, 놓기·모드 종료·UI 검증</t>
-  </si>
-  <si>
-    <t>7.05 Should 통합·초기화 회귀</t>
-  </si>
-  <si>
-    <t>FR-08/10/33
-TC-11/13/51, 미채택 기능은 제외 사유 기록</t>
-  </si>
-  <si>
-    <t>7.06 URDF 임포트·관절 매핑</t>
-  </si>
-  <si>
-    <t>FR-27
-가져온 팔로 커피 수행, 실패 시 기존 팔 유지</t>
-  </si>
-  <si>
-    <t>7.07 ROS2 송수신·연결 상태·폴백</t>
-  </si>
-  <si>
-    <t>FR-28
-목표 수신·상태 송신·단절 안내 및 로컬IK 복귀</t>
+    <t>7.01 (삭제) 최초 현관 웰컴 음성·자막</t>
+  </si>
+  <si>
+    <t>FR-08 삭제
+사운드 기능 제외(SRS v2.0), 작업 없음</t>
+  </si>
+  <si>
+    <t>7.02 (삭제) 온도·로봇 상태 안내</t>
+  </si>
+  <si>
+    <t>FR-10 삭제
+사운드 기능 제외(SRS v2.0), 작업 없음</t>
+  </si>
+  <si>
+    <t>7.03 (삭제) 로봇팔 직접 조종</t>
+  </si>
+  <si>
+    <t>FR-33 삭제
+직접 조종 없음, 로봇팔은 클릭 시 커피 만들기 시연만</t>
+  </si>
+  <si>
+    <t>7.04 (삭제) 직접 조종 버튼·그립</t>
+  </si>
+  <si>
+    <t>FR-33/34 삭제
+작업 없음</t>
+  </si>
+  <si>
+    <t>7.05 (삭제) Should 통합</t>
+  </si>
+  <si>
+    <t>Should 0개(SRS v2.4), 작업 없음
+초기화 회귀는 4.17·4.18에서 확인</t>
+  </si>
+  <si>
+    <t>7.06 (삭제) URDF 임포트</t>
+  </si>
+  <si>
+    <t>FR-27 삭제
+자체 로봇팔 모델로 시연(SRS v2.5), 작업 없음</t>
+  </si>
+  <si>
+    <t>7.07 (삭제) ROS2 연동</t>
+  </si>
+  <si>
+    <t>FR-28 삭제
+ROS2 연동 제외(SRS v2.2), 작업 없음</t>
   </si>
   <si>
     <t>7.08 URDF·ROS 통합 검증</t>

--- a/docs/WBS_모델하우스_컨피규레이터.xlsx
+++ b/docs/WBS_모델하우스_컨피규레이터.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">기획·설계</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01 SRS 범위 및 Must 확정 (v2.6: 13개)</t>
+    <t xml:space="preserve">1.01 SRS 범위 및 Must 확정 (v2.7: 13개)</t>
   </si>
   <si>
     <t xml:space="preserve">권오민</t>
@@ -139,7 +139,8 @@
   </si>
   <si>
     <t xml:space="preserve">전체
-삭제 요구사항 제외, FR-29 하위 7개와 부모 중복 집계 없음</t>
+삭제 요구사항 제외, FR-29 하위 7개와 부모 중복 집계 없음
+v2.7: 강사 피드백(정지·일시정지·옵션 초기화) 반영</t>
   </si>
   <si>
     <t xml:space="preserve">완료</t>
@@ -243,7 +244,8 @@
   </si>
   <si>
     <t xml:space="preserve">NFR-10
-Forward+ 및 구역별 반사 프로브 구성</t>
+Forward+ 및 구역별 반사 프로브 구성
+거울 프로브 Custom 유지·중복 정리 (10/12)</t>
   </si>
   <si>
     <t xml:space="preserve">2.11 첫날 프리팹 전달·Main 통합</t>
@@ -295,7 +297,8 @@
   </si>
   <si>
     <t xml:space="preserve">FR-04/05
-입실1초, 퇴실3초 대기+1초 감광</t>
+입실1초, 퇴실3초 대기+1초 감광
+LightFader 공통 클래스, 4개 구역 조명 5개 (10/12)</t>
   </si>
   <si>
     <t xml:space="preserve">3.06 (삭제) 중문 자동 개폐</t>
@@ -448,7 +451,8 @@
   </si>
   <si>
     <t xml:space="preserve">FR-30
-A-8 시각표, 버튼 누르고 1초 이내 반영, 보간 없음</t>
+A-8 시각표, 버튼 누르고 1초 이내 반영, 보간 없음
+로봇팔이 시간대마다 색이 바뀌던 문제 수정 (10/12)</t>
   </si>
   <si>
     <t xml:space="preserve">4.10 구역 조도 계산·조명 합산</t>
@@ -469,7 +473,8 @@
   </si>
   <si>
     <t xml:space="preserve">FR-25
-밀리초 시각·대상·내용, 센서와 동작 구분</t>
+밀리초 시각·대상·내용, 센서와 동작 구분
+기록 저장은 EventLogger, 패널은 표시만 (10/12)</t>
   </si>
   <si>
     <t xml:space="preserve">4.13 최신순 로그 패널·갱신 구현</t>
@@ -483,7 +488,8 @@
   </si>
   <si>
     <t xml:space="preserve">FR-13/15
-커피 중·완료 3초 이내 클릭 무시, 실패 후 홈</t>
+커피 중·완료 3초 이내 클릭 무시, 실패 후 홈
+피드백(10/12): C 동작·X 일시정지·Z 정지(든 컵 제자리), 근접 조작 패널·식탁 안내판</t>
   </si>
   <si>
     <t xml:space="preserve">4.15 커피 로봇팔 클릭 시연 흐름</t>
@@ -511,7 +517,8 @@
   </si>
   <si>
     <t xml:space="preserve">FR-26
-현관 이동·12시·패널 닫힘, 옵션과 비용 유지</t>
+현관 이동·12시·패널 닫힘, 옵션과 비용 유지
+[위치 초기화] 이름 변경, [옵션 초기화] 버튼(기본 옵션·0원) (10/12)</t>
   </si>
   <si>
     <t xml:space="preserve">4.19 시작·리셋 후 현관 재실 재평가</t>
@@ -525,20 +532,16 @@
   </si>
   <si>
     <t xml:space="preserve">FR-15
-아일랜드3곳·머신 통과, 도달 불가 실패 처리</t>
-  </si>
-  <si>
-    <t xml:space="preserve">진행 중</t>
+아일랜드3곳·머신 통과, 도달 불가 실패 처리
+10/13 자동 점검 통과: 보관대 3컵·추출구, 0.70m 컵 → 작업 실패 → 보관대·홈 (TC-18)</t>
   </si>
   <si>
     <t xml:space="preserve">4.21 퇴실·재진입 경계 시험</t>
   </si>
   <si>
     <t xml:space="preserve">FR-04/05
-2초·3.5초 재진입 검증</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미착수</t>
+2초·3.5초 재진입 검증
+10/13 자동 점검 통과: 2초 재진입 유지, 3.5초 재진입 0.52초에 100% (TC-05/06/07)</t>
   </si>
   <si>
     <t xml:space="preserve">4.22 필수 기능 전체 시나리오 점검</t>
@@ -555,7 +558,8 @@
   </si>
   <si>
     <t xml:space="preserve">Must 전체
-MVP를 막는 결함 해결 또는 영향·담당 기록</t>
+MVP를 막는 결함 해결 또는 영향·담당 기록
+코드 리뷰 반영 PR #7·#8·#9 머지 (10/12)</t>
   </si>
   <si>
     <t xml:space="preserve">4.24 선택 기능 채택 여부 판단·PR 마감</t>
@@ -575,11 +579,15 @@
 필수 사용자 흐름 통과,12:20 이전 종료</t>
   </si>
   <si>
+    <t xml:space="preserve">미착수</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.02 커피·센서·초기화 회귀와 수정</t>
   </si>
   <si>
     <t xml:space="preserve">FR-04/05/07/13/15/25/26/30
-전체 커피30초 이내,12:20 이전 종료</t>
+전체 커피30초 이내,12:20 이전 종료
+10/13 QA 자동 점검(Tools → COM → QA 자동 점검) 22/22 통과</t>
   </si>
   <si>
     <t xml:space="preserve">5.03 12:30 기능 동결·태그 확정</t>
@@ -607,7 +615,8 @@
   </si>
   <si>
     <t xml:space="preserve">NFR-02
-입실부터 동작 시작0.5초 이내, 의도된 지연 별도</t>
+입실부터 동작 시작0.5초 이내, 의도된 지연 별도
+10/13 방 진입 → 조명 켜기 시작 1ms (TC-38)</t>
   </si>
   <si>
     <t xml:space="preserve">5.07 데이터 소스·로봇 교체 시험</t>
@@ -681,6 +690,9 @@
   <si>
     <t xml:space="preserve">문서
 Unity6000.4.0f1 및 실제 채택 기능·에셋 경로 반영</t>
+  </si>
+  <si>
+    <t xml:space="preserve">진행 중</t>
   </si>
   <si>
     <t xml:space="preserve">6.06 SRS·WBS·TC·잔여 결함 정합성 검토</t>
@@ -1527,7 +1539,7 @@
         <v>1</v>
       </c>
       <c r="L1" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="M1" s="5" t="str">
         <f aca="false">"실적 미입력 "&amp;(83-COUNT(T6:T88))&amp;" / 83건"</f>
@@ -1544,11 +1556,11 @@
       </c>
       <c r="U1" s="6" t="n">
         <f aca="false">IF(OR(U5="",S5=0),"",U5/S5)</f>
-        <v>0.999610709262608</v>
+        <v>0.850182925940502</v>
       </c>
       <c r="V1" s="2" t="str">
         <f aca="false">IF(U1="","미확인",IF(U1&lt;0.75,"위험",IF(U1&lt;0.85,"경고",IF(U1&lt;0.95,"주의","양호"))))</f>
-        <v>양호</v>
+        <v>주의</v>
       </c>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
@@ -1746,7 +1758,7 @@
       </c>
       <c r="N5" s="10" t="n">
         <f aca="false">IF(COUNT(N6:N88)=0,"",MAX(N6:N88))</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="O5" s="11" t="n">
         <f aca="false">SUM(O6:O88)</f>
@@ -1754,31 +1766,31 @@
       </c>
       <c r="P5" s="11" t="n">
         <f aca="false">IF(COUNT(P6:P88)=0,"",SUM(P6:P88))</f>
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="Q5" s="11" t="n">
         <f aca="false">SUM(Q6:Q88)</f>
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="R5" s="11" t="n">
         <f aca="false">IF(COUNT(R6:R88)=0,"",SUM(R6:R88))</f>
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="S5" s="12" t="n">
         <f aca="false">AVERAGE(S6:S10)*C6+AVERAGE(S11:S22)*C11+AVERAGE(S23:S39)*C23+AVERAGE(S40:S63)*C40+AVERAGE(S64:S74)*C64+AVERAGE(S75:S88)*C75</f>
-        <v>0.652892561983471</v>
+        <v>0.818181818181818</v>
       </c>
       <c r="T5" s="12" t="n">
         <f aca="false">IF(COUNT(T6:T88)&lt;83,"",AVERAGE(T6:T88))</f>
-        <v>0.689759036144578</v>
+        <v>0.731927710843374</v>
       </c>
       <c r="U5" s="12" t="n">
         <f aca="false">IF(COUNT(T6:T88)&lt;83,"",AVERAGE(T6:T10)*C6+AVERAGE(T11:T22)*C11+AVERAGE(T23:T39)*C23+AVERAGE(T40:T63)*C40+AVERAGE(T64:T74)*C64+AVERAGE(T75:T88)*C75)</f>
-        <v>0.652638396956579</v>
+        <v>0.695604212133138</v>
       </c>
       <c r="V5" s="12" t="n">
         <f aca="false">IF(U5="","",U5-S5)</f>
-        <v>-0.000254165026892239</v>
+        <v>-0.12257760604868</v>
       </c>
       <c r="W5" s="13" t="n">
         <v>46301</v>
@@ -1811,7 +1823,7 @@
       <c r="AG5" s="9"/>
       <c r="AH5" s="9"/>
     </row>
-    <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="14" t="n">
         <v>1</v>
@@ -3293,7 +3305,7 @@
       <c r="AG19" s="26"/>
       <c r="AH19" s="26"/>
     </row>
-    <row r="20" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -4034,7 +4046,7 @@
       <c r="AG26" s="26"/>
       <c r="AH26" s="26"/>
     </row>
-    <row r="27" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -6245,7 +6257,7 @@
       <c r="AG47" s="26"/>
       <c r="AH47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -6560,7 +6572,7 @@
       <c r="AG50" s="26"/>
       <c r="AH50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -6770,7 +6782,7 @@
       <c r="AG52" s="26"/>
       <c r="AH52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -7190,7 +7202,7 @@
       <c r="AG56" s="26"/>
       <c r="AH56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -7400,7 +7412,7 @@
       <c r="AG58" s="26"/>
       <c r="AH58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -7428,14 +7440,16 @@
       <c r="M59" s="34" t="n">
         <v>46307</v>
       </c>
-      <c r="N59" s="34"/>
+      <c r="N59" s="34" t="n">
+        <v>46308</v>
+      </c>
       <c r="O59" s="29" t="n">
         <f aca="false">IF(OR(K59="",L59=""),"",IF(L59&lt;K59,"날짜 확인",NETWORKDAYS(K59,L59,휴일!$A$2:$A$2)))</f>
         <v>1</v>
       </c>
-      <c r="P59" s="29" t="str">
+      <c r="P59" s="29" t="n">
         <f aca="false">IF(OR(M59="",N59=""),"",IF(N59&lt;M59,"날짜 확인",NETWORKDAYS(M59,N59,휴일!$A$2:$A$2)))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q59" s="29" t="n">
         <f aca="false">IF(O59="","",IF($L$1&lt;K59,0,NETWORKDAYS(K59,MIN($L$1,L59),휴일!$A$2:$A$2)))</f>
@@ -7443,7 +7457,7 @@
       </c>
       <c r="R59" s="29" t="n">
         <f aca="false">IF(M59="","",IF($L$1&lt;M59,0,NETWORKDAYS(M59,IF(N59="",$L$1,MIN($L$1,N59)),휴일!$A$2:$A$2)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S59" s="30" t="n">
         <f aca="false">IF(O59="","",IF(O59=0,0,Q59/O59))</f>
@@ -7451,15 +7465,15 @@
       </c>
       <c r="T59" s="31" t="n">
         <f aca="false">IF(OR(AND(AG59&lt;&gt;"",OR(NOT(ISNUMBER(AG59)),AG59&lt;=0)),AND(AH59&lt;&gt;"",OR(NOT(ISNUMBER(AH59)),AH59&lt;0)),AND(ISNUMBER(AG59),ISNUMBER(AH59),AH59&gt;AG59)),"수량 확인",IF(AF59="완료",1,IF(AF59="미착수",0,IF(AND(ISNUMBER(AG59),ISNUMBER(AH59)),AH59/AG59,""))))</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U59" s="30" t="n">
         <f aca="false">IF(T59="","",T59)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="V59" s="30" t="n">
         <f aca="false">IF(OR(U59="",S59=""),"",U59-S59)</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="W59" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M59),W$5&gt;=$M59,W$5&lt;=IF($N59="",$L$1,$N59),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K59),W$5&gt;=$K59,W$5&lt;=$L59,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -7489,32 +7503,28 @@
         <f aca="false">IF(AND(ISNUMBER($M59),AC$5&gt;=$M59,AC$5&lt;=IF($N59="",$L$1,$N59),WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),2,IF(AND(ISNUMBER($K59),AC$5&gt;=$K59,AC$5&lt;=$L59,WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),1,""))</f>
         <v>2</v>
       </c>
-      <c r="AD59" s="32" t="str">
+      <c r="AD59" s="32" t="n">
         <f aca="false">IF(AND(ISNUMBER($M59),AD$5&gt;=$M59,AD$5&lt;=IF($N59="",$L$1,$N59),WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),2,IF(AND(ISNUMBER($K59),AD$5&gt;=$K59,AD$5&lt;=$L59,WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),1,""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE59" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M59),AE$5&gt;=$M59,AE$5&lt;=IF($N59="",$L$1,$N59),WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),2,IF(AND(ISNUMBER($K59),AE$5&gt;=$K59,AE$5&lt;=$L59,WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),1,""))</f>
         <v/>
       </c>
       <c r="AF59" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="AG59" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH59" s="26" t="n">
-        <v>1</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="AG59" s="26"/>
+      <c r="AH59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="16"/>
       <c r="E60" s="16"/>
       <c r="F60" s="27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G60" s="27"/>
       <c r="H60" s="27" t="s">
@@ -7524,7 +7534,7 @@
         <v>33</v>
       </c>
       <c r="J60" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K60" s="28" t="n">
         <v>46307</v>
@@ -7532,23 +7542,27 @@
       <c r="L60" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="M60" s="34"/>
-      <c r="N60" s="34"/>
+      <c r="M60" s="34" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N60" s="34" t="n">
+        <v>46308</v>
+      </c>
       <c r="O60" s="29" t="n">
         <f aca="false">IF(OR(K60="",L60=""),"",IF(L60&lt;K60,"날짜 확인",NETWORKDAYS(K60,L60,휴일!$A$2:$A$2)))</f>
         <v>1</v>
       </c>
-      <c r="P60" s="29" t="str">
+      <c r="P60" s="29" t="n">
         <f aca="false">IF(OR(M60="",N60=""),"",IF(N60&lt;M60,"날짜 확인",NETWORKDAYS(M60,N60,휴일!$A$2:$A$2)))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Q60" s="29" t="n">
         <f aca="false">IF(O60="","",IF($L$1&lt;K60,0,NETWORKDAYS(K60,MIN($L$1,L60),휴일!$A$2:$A$2)))</f>
         <v>1</v>
       </c>
-      <c r="R60" s="29" t="str">
+      <c r="R60" s="29" t="n">
         <f aca="false">IF(M60="","",IF($L$1&lt;M60,0,NETWORKDAYS(M60,IF(N60="",$L$1,MIN($L$1,N60)),휴일!$A$2:$A$2)))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S60" s="30" t="n">
         <f aca="false">IF(O60="","",IF(O60=0,0,Q60/O60))</f>
@@ -7556,15 +7570,15 @@
       </c>
       <c r="T60" s="31" t="n">
         <f aca="false">IF(OR(AND(AG60&lt;&gt;"",OR(NOT(ISNUMBER(AG60)),AG60&lt;=0)),AND(AH60&lt;&gt;"",OR(NOT(ISNUMBER(AH60)),AH60&lt;0)),AND(ISNUMBER(AG60),ISNUMBER(AH60),AH60&gt;AG60)),"수량 확인",IF(AF60="완료",1,IF(AF60="미착수",0,IF(AND(ISNUMBER(AG60),ISNUMBER(AH60)),AH60/AG60,""))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U60" s="30" t="n">
         <f aca="false">IF(T60="","",T60)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="30" t="n">
         <f aca="false">IF(OR(U60="",S60=""),"",U60-S60)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W60" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M60),W$5&gt;=$M60,W$5&lt;=IF($N60="",$L$1,$N60),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K60),W$5&gt;=$K60,W$5&lt;=$L60,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -7594,16 +7608,16 @@
         <f aca="false">IF(AND(ISNUMBER($M60),AC$5&gt;=$M60,AC$5&lt;=IF($N60="",$L$1,$N60),WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),2,IF(AND(ISNUMBER($K60),AC$5&gt;=$K60,AC$5&lt;=$L60,WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),1,""))</f>
         <v>1</v>
       </c>
-      <c r="AD60" s="32" t="str">
+      <c r="AD60" s="32" t="n">
         <f aca="false">IF(AND(ISNUMBER($M60),AD$5&gt;=$M60,AD$5&lt;=IF($N60="",$L$1,$N60),WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),2,IF(AND(ISNUMBER($K60),AD$5&gt;=$K60,AD$5&lt;=$L60,WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),1,""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE60" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M60),AE$5&gt;=$M60,AE$5&lt;=IF($N60="",$L$1,$N60),WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),2,IF(AND(ISNUMBER($K60),AE$5&gt;=$K60,AE$5&lt;=$L60,WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),1,""))</f>
         <v/>
       </c>
       <c r="AF60" s="25" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="AG60" s="26"/>
       <c r="AH60" s="26"/>
@@ -7615,7 +7629,7 @@
       <c r="D61" s="16"/>
       <c r="E61" s="16"/>
       <c r="F61" s="27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G61" s="27"/>
       <c r="H61" s="27" t="s">
@@ -7625,7 +7639,7 @@
         <v>34</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K61" s="28" t="n">
         <v>46307</v>
@@ -7651,7 +7665,7 @@
       </c>
       <c r="R61" s="29" t="n">
         <f aca="false">IF(M61="","",IF($L$1&lt;M61,0,NETWORKDAYS(M61,IF(N61="",$L$1,MIN($L$1,N61)),휴일!$A$2:$A$2)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S61" s="30" t="n">
         <f aca="false">IF(O61="","",IF(O61=0,0,Q61/O61))</f>
@@ -7697,16 +7711,16 @@
         <f aca="false">IF(AND(ISNUMBER($M61),AC$5&gt;=$M61,AC$5&lt;=IF($N61="",$L$1,$N61),WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),2,IF(AND(ISNUMBER($K61),AC$5&gt;=$K61,AC$5&lt;=$L61,WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),1,""))</f>
         <v>2</v>
       </c>
-      <c r="AD61" s="32" t="str">
+      <c r="AD61" s="32" t="n">
         <f aca="false">IF(AND(ISNUMBER($M61),AD$5&gt;=$M61,AD$5&lt;=IF($N61="",$L$1,$N61),WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),2,IF(AND(ISNUMBER($K61),AD$5&gt;=$K61,AD$5&lt;=$L61,WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),1,""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE61" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M61),AE$5&gt;=$M61,AE$5&lt;=IF($N61="",$L$1,$N61),WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),2,IF(AND(ISNUMBER($K61),AE$5&gt;=$K61,AE$5&lt;=$L61,WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),1,""))</f>
         <v/>
       </c>
       <c r="AF61" s="25" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG61" s="26" t="n">
         <v>12</v>
@@ -7715,14 +7729,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
       <c r="F62" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G62" s="27"/>
       <c r="H62" s="27" t="s">
@@ -7732,7 +7746,7 @@
         <v>33</v>
       </c>
       <c r="J62" s="27" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K62" s="28" t="n">
         <v>46307</v>
@@ -7827,7 +7841,7 @@
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G63" s="27"/>
       <c r="H63" s="27" t="s">
@@ -7837,7 +7851,7 @@
         <v>34</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K63" s="28" t="n">
         <v>46307</v>
@@ -7934,11 +7948,11 @@
         <v>0.165289256198347</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E64" s="16"/>
       <c r="F64" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G64" s="17"/>
       <c r="H64" s="17" t="s">
@@ -7948,7 +7962,7 @@
         <v>34</v>
       </c>
       <c r="J64" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K64" s="18" t="n">
         <v>46308</v>
@@ -7968,7 +7982,7 @@
       </c>
       <c r="Q64" s="20" t="n">
         <f aca="false">IF(O64="","",IF($L$1&lt;K64,0,NETWORKDAYS(K64,MIN($L$1,L64),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="20" t="str">
         <f aca="false">IF(M64="","",IF($L$1&lt;M64,0,NETWORKDAYS(M64,IF(N64="",$L$1,MIN($L$1,N64)),휴일!$A$2:$A$2)))</f>
@@ -7976,7 +7990,7 @@
       </c>
       <c r="S64" s="21" t="n">
         <f aca="false">IF(O64="","",IF(O64=0,0,Q64/O64))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="22" t="n">
         <f aca="false">IF(OR(AND(AG64&lt;&gt;"",OR(NOT(ISNUMBER(AG64)),AG64&lt;=0)),AND(AH64&lt;&gt;"",OR(NOT(ISNUMBER(AH64)),AH64&lt;0)),AND(ISNUMBER(AG64),ISNUMBER(AH64),AH64&gt;AG64)),"수량 확인",IF(AF64="완료",1,IF(AF64="미착수",0,IF(AND(ISNUMBER(AG64),ISNUMBER(AH64)),AH64/AG64,""))))</f>
@@ -7988,7 +8002,7 @@
       </c>
       <c r="V64" s="21" t="n">
         <f aca="false">IF(OR(U64="",S64=""),"",U64-S64)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W64" s="23" t="str">
         <f aca="false">IF(AND(ISNUMBER($M64),W$5&gt;=$M64,W$5&lt;=IF($N64="",$L$1,$N64),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K64),W$5&gt;=$K64,W$5&lt;=$L64,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -8027,19 +8041,19 @@
         <v/>
       </c>
       <c r="AF64" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG64" s="26"/>
       <c r="AH64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
       <c r="F65" s="27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G65" s="27"/>
       <c r="H65" s="27" t="s">
@@ -8049,7 +8063,7 @@
         <v>33</v>
       </c>
       <c r="J65" s="27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K65" s="28" t="n">
         <v>46308</v>
@@ -8057,35 +8071,39 @@
       <c r="L65" s="28" t="n">
         <v>46308</v>
       </c>
-      <c r="M65" s="34"/>
-      <c r="N65" s="34"/>
+      <c r="M65" s="34" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N65" s="34" t="n">
+        <v>46308</v>
+      </c>
       <c r="O65" s="29" t="n">
         <f aca="false">IF(OR(K65="",L65=""),"",IF(L65&lt;K65,"날짜 확인",NETWORKDAYS(K65,L65,휴일!$A$2:$A$2)))</f>
         <v>1</v>
       </c>
-      <c r="P65" s="29" t="str">
+      <c r="P65" s="29" t="n">
         <f aca="false">IF(OR(M65="",N65=""),"",IF(N65&lt;M65,"날짜 확인",NETWORKDAYS(M65,N65,휴일!$A$2:$A$2)))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Q65" s="29" t="n">
         <f aca="false">IF(O65="","",IF($L$1&lt;K65,0,NETWORKDAYS(K65,MIN($L$1,L65),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
-      </c>
-      <c r="R65" s="29" t="str">
+        <v>1</v>
+      </c>
+      <c r="R65" s="29" t="n">
         <f aca="false">IF(M65="","",IF($L$1&lt;M65,0,NETWORKDAYS(M65,IF(N65="",$L$1,MIN($L$1,N65)),휴일!$A$2:$A$2)))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S65" s="30" t="n">
         <f aca="false">IF(O65="","",IF(O65=0,0,Q65/O65))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="31" t="n">
         <f aca="false">IF(OR(AND(AG65&lt;&gt;"",OR(NOT(ISNUMBER(AG65)),AG65&lt;=0)),AND(AH65&lt;&gt;"",OR(NOT(ISNUMBER(AH65)),AH65&lt;0)),AND(ISNUMBER(AG65),ISNUMBER(AH65),AH65&gt;AG65)),"수량 확인",IF(AF65="완료",1,IF(AF65="미착수",0,IF(AND(ISNUMBER(AG65),ISNUMBER(AH65)),AH65/AG65,""))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U65" s="30" t="n">
         <f aca="false">IF(T65="","",T65)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V65" s="30" t="n">
         <f aca="false">IF(OR(U65="",S65=""),"",U65-S65)</f>
@@ -8121,14 +8139,14 @@
       </c>
       <c r="AD65" s="32" t="n">
         <f aca="false">IF(AND(ISNUMBER($M65),AD$5&gt;=$M65,AD$5&lt;=IF($N65="",$L$1,$N65),WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),2,IF(AND(ISNUMBER($K65),AD$5&gt;=$K65,AD$5&lt;=$L65,WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),1,""))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE65" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M65),AE$5&gt;=$M65,AE$5&lt;=IF($N65="",$L$1,$N65),WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),2,IF(AND(ISNUMBER($K65),AE$5&gt;=$K65,AE$5&lt;=$L65,WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),1,""))</f>
         <v/>
       </c>
       <c r="AF65" s="25" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="AG65" s="26"/>
       <c r="AH65" s="26"/>
@@ -8140,7 +8158,7 @@
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
       <c r="F66" s="27" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G66" s="27"/>
       <c r="H66" s="27" t="s">
@@ -8150,7 +8168,7 @@
         <v>34</v>
       </c>
       <c r="J66" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K66" s="28" t="n">
         <v>46308</v>
@@ -8170,7 +8188,7 @@
       </c>
       <c r="Q66" s="29" t="n">
         <f aca="false">IF(O66="","",IF($L$1&lt;K66,0,NETWORKDAYS(K66,MIN($L$1,L66),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="29" t="str">
         <f aca="false">IF(M66="","",IF($L$1&lt;M66,0,NETWORKDAYS(M66,IF(N66="",$L$1,MIN($L$1,N66)),휴일!$A$2:$A$2)))</f>
@@ -8178,7 +8196,7 @@
       </c>
       <c r="S66" s="30" t="n">
         <f aca="false">IF(O66="","",IF(O66=0,0,Q66/O66))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="31" t="n">
         <f aca="false">IF(OR(AND(AG66&lt;&gt;"",OR(NOT(ISNUMBER(AG66)),AG66&lt;=0)),AND(AH66&lt;&gt;"",OR(NOT(ISNUMBER(AH66)),AH66&lt;0)),AND(ISNUMBER(AG66),ISNUMBER(AH66),AH66&gt;AG66)),"수량 확인",IF(AF66="완료",1,IF(AF66="미착수",0,IF(AND(ISNUMBER(AG66),ISNUMBER(AH66)),AH66/AG66,""))))</f>
@@ -8190,7 +8208,7 @@
       </c>
       <c r="V66" s="30" t="n">
         <f aca="false">IF(OR(U66="",S66=""),"",U66-S66)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W66" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M66),W$5&gt;=$M66,W$5&lt;=IF($N66="",$L$1,$N66),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K66),W$5&gt;=$K66,W$5&lt;=$L66,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -8229,7 +8247,7 @@
         <v/>
       </c>
       <c r="AF66" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG66" s="26"/>
       <c r="AH66" s="26"/>
@@ -8241,7 +8259,7 @@
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
       <c r="F67" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G67" s="27"/>
       <c r="H67" s="27" t="s">
@@ -8251,7 +8269,7 @@
         <v>34</v>
       </c>
       <c r="J67" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K67" s="28" t="n">
         <v>46308</v>
@@ -8271,7 +8289,7 @@
       </c>
       <c r="Q67" s="29" t="n">
         <f aca="false">IF(O67="","",IF($L$1&lt;K67,0,NETWORKDAYS(K67,MIN($L$1,L67),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="29" t="str">
         <f aca="false">IF(M67="","",IF($L$1&lt;M67,0,NETWORKDAYS(M67,IF(N67="",$L$1,MIN($L$1,N67)),휴일!$A$2:$A$2)))</f>
@@ -8279,7 +8297,7 @@
       </c>
       <c r="S67" s="30" t="n">
         <f aca="false">IF(O67="","",IF(O67=0,0,Q67/O67))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="31" t="n">
         <f aca="false">IF(OR(AND(AG67&lt;&gt;"",OR(NOT(ISNUMBER(AG67)),AG67&lt;=0)),AND(AH67&lt;&gt;"",OR(NOT(ISNUMBER(AH67)),AH67&lt;0)),AND(ISNUMBER(AG67),ISNUMBER(AH67),AH67&gt;AG67)),"수량 확인",IF(AF67="완료",1,IF(AF67="미착수",0,IF(AND(ISNUMBER(AG67),ISNUMBER(AH67)),AH67/AG67,""))))</f>
@@ -8291,7 +8309,7 @@
       </c>
       <c r="V67" s="30" t="n">
         <f aca="false">IF(OR(U67="",S67=""),"",U67-S67)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W67" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M67),W$5&gt;=$M67,W$5&lt;=IF($N67="",$L$1,$N67),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K67),W$5&gt;=$K67,W$5&lt;=$L67,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -8330,7 +8348,7 @@
         <v/>
       </c>
       <c r="AF67" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG67" s="26"/>
       <c r="AH67" s="26"/>
@@ -8342,7 +8360,7 @@
       <c r="D68" s="16"/>
       <c r="E68" s="16"/>
       <c r="F68" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G68" s="27"/>
       <c r="H68" s="27" t="s">
@@ -8352,7 +8370,7 @@
         <v>33</v>
       </c>
       <c r="J68" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K68" s="28" t="n">
         <v>46308</v>
@@ -8372,7 +8390,7 @@
       </c>
       <c r="Q68" s="29" t="n">
         <f aca="false">IF(O68="","",IF($L$1&lt;K68,0,NETWORKDAYS(K68,MIN($L$1,L68),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="29" t="str">
         <f aca="false">IF(M68="","",IF($L$1&lt;M68,0,NETWORKDAYS(M68,IF(N68="",$L$1,MIN($L$1,N68)),휴일!$A$2:$A$2)))</f>
@@ -8380,7 +8398,7 @@
       </c>
       <c r="S68" s="30" t="n">
         <f aca="false">IF(O68="","",IF(O68=0,0,Q68/O68))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="31" t="n">
         <f aca="false">IF(OR(AND(AG68&lt;&gt;"",OR(NOT(ISNUMBER(AG68)),AG68&lt;=0)),AND(AH68&lt;&gt;"",OR(NOT(ISNUMBER(AH68)),AH68&lt;0)),AND(ISNUMBER(AG68),ISNUMBER(AH68),AH68&gt;AG68)),"수량 확인",IF(AF68="완료",1,IF(AF68="미착수",0,IF(AND(ISNUMBER(AG68),ISNUMBER(AH68)),AH68/AG68,""))))</f>
@@ -8392,7 +8410,7 @@
       </c>
       <c r="V68" s="30" t="n">
         <f aca="false">IF(OR(U68="",S68=""),"",U68-S68)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W68" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M68),W$5&gt;=$M68,W$5&lt;=IF($N68="",$L$1,$N68),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K68),W$5&gt;=$K68,W$5&lt;=$L68,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -8431,19 +8449,19 @@
         <v/>
       </c>
       <c r="AF68" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG68" s="26"/>
       <c r="AH68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="16"/>
       <c r="E69" s="16"/>
       <c r="F69" s="27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G69" s="27"/>
       <c r="H69" s="27" t="s">
@@ -8453,7 +8471,7 @@
         <v>33</v>
       </c>
       <c r="J69" s="27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K69" s="28" t="n">
         <v>46308</v>
@@ -8461,35 +8479,39 @@
       <c r="L69" s="28" t="n">
         <v>46308</v>
       </c>
-      <c r="M69" s="34"/>
-      <c r="N69" s="34"/>
+      <c r="M69" s="34" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N69" s="34" t="n">
+        <v>46308</v>
+      </c>
       <c r="O69" s="29" t="n">
         <f aca="false">IF(OR(K69="",L69=""),"",IF(L69&lt;K69,"날짜 확인",NETWORKDAYS(K69,L69,휴일!$A$2:$A$2)))</f>
         <v>1</v>
       </c>
-      <c r="P69" s="29" t="str">
+      <c r="P69" s="29" t="n">
         <f aca="false">IF(OR(M69="",N69=""),"",IF(N69&lt;M69,"날짜 확인",NETWORKDAYS(M69,N69,휴일!$A$2:$A$2)))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Q69" s="29" t="n">
         <f aca="false">IF(O69="","",IF($L$1&lt;K69,0,NETWORKDAYS(K69,MIN($L$1,L69),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
-      </c>
-      <c r="R69" s="29" t="str">
+        <v>1</v>
+      </c>
+      <c r="R69" s="29" t="n">
         <f aca="false">IF(M69="","",IF($L$1&lt;M69,0,NETWORKDAYS(M69,IF(N69="",$L$1,MIN($L$1,N69)),휴일!$A$2:$A$2)))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S69" s="30" t="n">
         <f aca="false">IF(O69="","",IF(O69=0,0,Q69/O69))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="31" t="n">
         <f aca="false">IF(OR(AND(AG69&lt;&gt;"",OR(NOT(ISNUMBER(AG69)),AG69&lt;=0)),AND(AH69&lt;&gt;"",OR(NOT(ISNUMBER(AH69)),AH69&lt;0)),AND(ISNUMBER(AG69),ISNUMBER(AH69),AH69&gt;AG69)),"수량 확인",IF(AF69="완료",1,IF(AF69="미착수",0,IF(AND(ISNUMBER(AG69),ISNUMBER(AH69)),AH69/AG69,""))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U69" s="30" t="n">
         <f aca="false">IF(T69="","",T69)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V69" s="30" t="n">
         <f aca="false">IF(OR(U69="",S69=""),"",U69-S69)</f>
@@ -8525,14 +8547,14 @@
       </c>
       <c r="AD69" s="32" t="n">
         <f aca="false">IF(AND(ISNUMBER($M69),AD$5&gt;=$M69,AD$5&lt;=IF($N69="",$L$1,$N69),WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),2,IF(AND(ISNUMBER($K69),AD$5&gt;=$K69,AD$5&lt;=$L69,WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),1,""))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE69" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M69),AE$5&gt;=$M69,AE$5&lt;=IF($N69="",$L$1,$N69),WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),2,IF(AND(ISNUMBER($K69),AE$5&gt;=$K69,AE$5&lt;=$L69,WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),1,""))</f>
         <v/>
       </c>
       <c r="AF69" s="25" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="AG69" s="26"/>
       <c r="AH69" s="26"/>
@@ -8544,7 +8566,7 @@
       <c r="D70" s="16"/>
       <c r="E70" s="16"/>
       <c r="F70" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G70" s="27"/>
       <c r="H70" s="27" t="s">
@@ -8554,7 +8576,7 @@
         <v>33</v>
       </c>
       <c r="J70" s="27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K70" s="28" t="n">
         <v>46308</v>
@@ -8574,7 +8596,7 @@
       </c>
       <c r="Q70" s="29" t="n">
         <f aca="false">IF(O70="","",IF($L$1&lt;K70,0,NETWORKDAYS(K70,MIN($L$1,L70),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="29" t="str">
         <f aca="false">IF(M70="","",IF($L$1&lt;M70,0,NETWORKDAYS(M70,IF(N70="",$L$1,MIN($L$1,N70)),휴일!$A$2:$A$2)))</f>
@@ -8582,7 +8604,7 @@
       </c>
       <c r="S70" s="30" t="n">
         <f aca="false">IF(O70="","",IF(O70=0,0,Q70/O70))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="31" t="n">
         <f aca="false">IF(OR(AND(AG70&lt;&gt;"",OR(NOT(ISNUMBER(AG70)),AG70&lt;=0)),AND(AH70&lt;&gt;"",OR(NOT(ISNUMBER(AH70)),AH70&lt;0)),AND(ISNUMBER(AG70),ISNUMBER(AH70),AH70&gt;AG70)),"수량 확인",IF(AF70="완료",1,IF(AF70="미착수",0,IF(AND(ISNUMBER(AG70),ISNUMBER(AH70)),AH70/AG70,""))))</f>
@@ -8594,7 +8616,7 @@
       </c>
       <c r="V70" s="30" t="n">
         <f aca="false">IF(OR(U70="",S70=""),"",U70-S70)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W70" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M70),W$5&gt;=$M70,W$5&lt;=IF($N70="",$L$1,$N70),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K70),W$5&gt;=$K70,W$5&lt;=$L70,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -8633,7 +8655,7 @@
         <v/>
       </c>
       <c r="AF70" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG70" s="26"/>
       <c r="AH70" s="26"/>
@@ -8645,7 +8667,7 @@
       <c r="D71" s="16"/>
       <c r="E71" s="16"/>
       <c r="F71" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G71" s="27"/>
       <c r="H71" s="27" t="s">
@@ -8655,7 +8677,7 @@
         <v>34</v>
       </c>
       <c r="J71" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K71" s="28" t="n">
         <v>46308</v>
@@ -8675,7 +8697,7 @@
       </c>
       <c r="Q71" s="29" t="n">
         <f aca="false">IF(O71="","",IF($L$1&lt;K71,0,NETWORKDAYS(K71,MIN($L$1,L71),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="29" t="str">
         <f aca="false">IF(M71="","",IF($L$1&lt;M71,0,NETWORKDAYS(M71,IF(N71="",$L$1,MIN($L$1,N71)),휴일!$A$2:$A$2)))</f>
@@ -8683,7 +8705,7 @@
       </c>
       <c r="S71" s="30" t="n">
         <f aca="false">IF(O71="","",IF(O71=0,0,Q71/O71))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" s="31" t="n">
         <f aca="false">IF(OR(AND(AG71&lt;&gt;"",OR(NOT(ISNUMBER(AG71)),AG71&lt;=0)),AND(AH71&lt;&gt;"",OR(NOT(ISNUMBER(AH71)),AH71&lt;0)),AND(ISNUMBER(AG71),ISNUMBER(AH71),AH71&gt;AG71)),"수량 확인",IF(AF71="완료",1,IF(AF71="미착수",0,IF(AND(ISNUMBER(AG71),ISNUMBER(AH71)),AH71/AG71,""))))</f>
@@ -8695,7 +8717,7 @@
       </c>
       <c r="V71" s="30" t="n">
         <f aca="false">IF(OR(U71="",S71=""),"",U71-S71)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W71" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M71),W$5&gt;=$M71,W$5&lt;=IF($N71="",$L$1,$N71),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K71),W$5&gt;=$K71,W$5&lt;=$L71,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -8734,7 +8756,7 @@
         <v/>
       </c>
       <c r="AF71" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG71" s="26"/>
       <c r="AH71" s="26"/>
@@ -8746,7 +8768,7 @@
       <c r="D72" s="16"/>
       <c r="E72" s="16"/>
       <c r="F72" s="27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G72" s="27"/>
       <c r="H72" s="27" t="s">
@@ -8756,7 +8778,7 @@
         <v>33</v>
       </c>
       <c r="J72" s="27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K72" s="28" t="n">
         <v>46308</v>
@@ -8776,7 +8798,7 @@
       </c>
       <c r="Q72" s="29" t="n">
         <f aca="false">IF(O72="","",IF($L$1&lt;K72,0,NETWORKDAYS(K72,MIN($L$1,L72),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="29" t="str">
         <f aca="false">IF(M72="","",IF($L$1&lt;M72,0,NETWORKDAYS(M72,IF(N72="",$L$1,MIN($L$1,N72)),휴일!$A$2:$A$2)))</f>
@@ -8784,7 +8806,7 @@
       </c>
       <c r="S72" s="30" t="n">
         <f aca="false">IF(O72="","",IF(O72=0,0,Q72/O72))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="31" t="n">
         <f aca="false">IF(OR(AND(AG72&lt;&gt;"",OR(NOT(ISNUMBER(AG72)),AG72&lt;=0)),AND(AH72&lt;&gt;"",OR(NOT(ISNUMBER(AH72)),AH72&lt;0)),AND(ISNUMBER(AG72),ISNUMBER(AH72),AH72&gt;AG72)),"수량 확인",IF(AF72="완료",1,IF(AF72="미착수",0,IF(AND(ISNUMBER(AG72),ISNUMBER(AH72)),AH72/AG72,""))))</f>
@@ -8796,7 +8818,7 @@
       </c>
       <c r="V72" s="30" t="n">
         <f aca="false">IF(OR(U72="",S72=""),"",U72-S72)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W72" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M72),W$5&gt;=$M72,W$5&lt;=IF($N72="",$L$1,$N72),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K72),W$5&gt;=$K72,W$5&lt;=$L72,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -8835,7 +8857,7 @@
         <v/>
       </c>
       <c r="AF72" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG72" s="26"/>
       <c r="AH72" s="26"/>
@@ -8847,7 +8869,7 @@
       <c r="D73" s="16"/>
       <c r="E73" s="16"/>
       <c r="F73" s="27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G73" s="27"/>
       <c r="H73" s="27" t="s">
@@ -8857,7 +8879,7 @@
         <v>34</v>
       </c>
       <c r="J73" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K73" s="28" t="n">
         <v>46308</v>
@@ -8877,7 +8899,7 @@
       </c>
       <c r="Q73" s="29" t="n">
         <f aca="false">IF(O73="","",IF($L$1&lt;K73,0,NETWORKDAYS(K73,MIN($L$1,L73),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="29" t="str">
         <f aca="false">IF(M73="","",IF($L$1&lt;M73,0,NETWORKDAYS(M73,IF(N73="",$L$1,MIN($L$1,N73)),휴일!$A$2:$A$2)))</f>
@@ -8885,7 +8907,7 @@
       </c>
       <c r="S73" s="30" t="n">
         <f aca="false">IF(O73="","",IF(O73=0,0,Q73/O73))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="31" t="n">
         <f aca="false">IF(OR(AND(AG73&lt;&gt;"",OR(NOT(ISNUMBER(AG73)),AG73&lt;=0)),AND(AH73&lt;&gt;"",OR(NOT(ISNUMBER(AH73)),AH73&lt;0)),AND(ISNUMBER(AG73),ISNUMBER(AH73),AH73&gt;AG73)),"수량 확인",IF(AF73="완료",1,IF(AF73="미착수",0,IF(AND(ISNUMBER(AG73),ISNUMBER(AH73)),AH73/AG73,""))))</f>
@@ -8897,7 +8919,7 @@
       </c>
       <c r="V73" s="30" t="n">
         <f aca="false">IF(OR(U73="",S73=""),"",U73-S73)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W73" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M73),W$5&gt;=$M73,W$5&lt;=IF($N73="",$L$1,$N73),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K73),W$5&gt;=$K73,W$5&lt;=$L73,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -8936,7 +8958,7 @@
         <v/>
       </c>
       <c r="AF73" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG73" s="26"/>
       <c r="AH73" s="26"/>
@@ -8948,7 +8970,7 @@
       <c r="D74" s="16"/>
       <c r="E74" s="16"/>
       <c r="F74" s="27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G74" s="27"/>
       <c r="H74" s="27" t="s">
@@ -8958,7 +8980,7 @@
         <v>33</v>
       </c>
       <c r="J74" s="27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K74" s="28" t="n">
         <v>46308</v>
@@ -8978,7 +9000,7 @@
       </c>
       <c r="Q74" s="29" t="n">
         <f aca="false">IF(O74="","",IF($L$1&lt;K74,0,NETWORKDAYS(K74,MIN($L$1,L74),휴일!$A$2:$A$2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="29" t="str">
         <f aca="false">IF(M74="","",IF($L$1&lt;M74,0,NETWORKDAYS(M74,IF(N74="",$L$1,MIN($L$1,N74)),휴일!$A$2:$A$2)))</f>
@@ -8986,7 +9008,7 @@
       </c>
       <c r="S74" s="30" t="n">
         <f aca="false">IF(O74="","",IF(O74=0,0,Q74/O74))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="31" t="n">
         <f aca="false">IF(OR(AND(AG74&lt;&gt;"",OR(NOT(ISNUMBER(AG74)),AG74&lt;=0)),AND(AH74&lt;&gt;"",OR(NOT(ISNUMBER(AH74)),AH74&lt;0)),AND(ISNUMBER(AG74),ISNUMBER(AH74),AH74&gt;AG74)),"수량 확인",IF(AF74="완료",1,IF(AF74="미착수",0,IF(AND(ISNUMBER(AG74),ISNUMBER(AH74)),AH74/AG74,""))))</f>
@@ -8998,7 +9020,7 @@
       </c>
       <c r="V74" s="30" t="n">
         <f aca="false">IF(OR(U74="",S74=""),"",U74-S74)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W74" s="32" t="str">
         <f aca="false">IF(AND(ISNUMBER($M74),W$5&gt;=$M74,W$5&lt;=IF($N74="",$L$1,$N74),WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),2,IF(AND(ISNUMBER($K74),W$5&gt;=$K74,W$5&lt;=$L74,WEEKDAY(W$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,W$5)=0),1,""))</f>
@@ -9037,7 +9059,7 @@
         <v/>
       </c>
       <c r="AF74" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG74" s="26"/>
       <c r="AH74" s="26"/>
@@ -9051,11 +9073,11 @@
         <v>0.181818181818182</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E75" s="16"/>
       <c r="F75" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G75" s="17"/>
       <c r="H75" s="17" t="s">
@@ -9065,7 +9087,7 @@
         <v>33</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K75" s="18" t="n">
         <v>46309</v>
@@ -9144,7 +9166,7 @@
         <v>1</v>
       </c>
       <c r="AF75" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG75" s="26"/>
       <c r="AH75" s="26"/>
@@ -9156,7 +9178,7 @@
       <c r="D76" s="16"/>
       <c r="E76" s="16"/>
       <c r="F76" s="27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G76" s="27"/>
       <c r="H76" s="27" t="s">
@@ -9166,7 +9188,7 @@
         <v>33</v>
       </c>
       <c r="J76" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K76" s="28" t="n">
         <v>46309</v>
@@ -9245,7 +9267,7 @@
         <v>1</v>
       </c>
       <c r="AF76" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG76" s="26"/>
       <c r="AH76" s="26"/>
@@ -9257,7 +9279,7 @@
       <c r="D77" s="16"/>
       <c r="E77" s="16"/>
       <c r="F77" s="27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G77" s="27"/>
       <c r="H77" s="27" t="s">
@@ -9267,7 +9289,7 @@
         <v>34</v>
       </c>
       <c r="J77" s="27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K77" s="28" t="n">
         <v>46309</v>
@@ -9346,7 +9368,7 @@
         <v>1</v>
       </c>
       <c r="AF77" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG77" s="26"/>
       <c r="AH77" s="26"/>
@@ -9358,7 +9380,7 @@
       <c r="D78" s="16"/>
       <c r="E78" s="16"/>
       <c r="F78" s="27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G78" s="27"/>
       <c r="H78" s="27" t="s">
@@ -9368,7 +9390,7 @@
         <v>33</v>
       </c>
       <c r="J78" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K78" s="28" t="n">
         <v>46309</v>
@@ -9447,7 +9469,7 @@
         <v>1</v>
       </c>
       <c r="AF78" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG78" s="26"/>
       <c r="AH78" s="26"/>
@@ -9459,7 +9481,7 @@
       <c r="D79" s="16"/>
       <c r="E79" s="16"/>
       <c r="F79" s="27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G79" s="27"/>
       <c r="H79" s="27" t="s">
@@ -9469,7 +9491,7 @@
         <v>34</v>
       </c>
       <c r="J79" s="27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K79" s="28" t="n">
         <v>46309</v>
@@ -9495,7 +9517,7 @@
       </c>
       <c r="R79" s="29" t="n">
         <f aca="false">IF(M79="","",IF($L$1&lt;M79,0,NETWORKDAYS(M79,IF(N79="",$L$1,MIN($L$1,N79)),휴일!$A$2:$A$2)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S79" s="30" t="n">
         <f aca="false">IF(O79="","",IF(O79=0,0,Q79/O79))</f>
@@ -9541,16 +9563,16 @@
         <f aca="false">IF(AND(ISNUMBER($M79),AC$5&gt;=$M79,AC$5&lt;=IF($N79="",$L$1,$N79),WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),2,IF(AND(ISNUMBER($K79),AC$5&gt;=$K79,AC$5&lt;=$L79,WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),1,""))</f>
         <v>2</v>
       </c>
-      <c r="AD79" s="32" t="str">
+      <c r="AD79" s="32" t="n">
         <f aca="false">IF(AND(ISNUMBER($M79),AD$5&gt;=$M79,AD$5&lt;=IF($N79="",$L$1,$N79),WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),2,IF(AND(ISNUMBER($K79),AD$5&gt;=$K79,AD$5&lt;=$L79,WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),1,""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE79" s="32" t="n">
         <f aca="false">IF(AND(ISNUMBER($M79),AE$5&gt;=$M79,AE$5&lt;=IF($N79="",$L$1,$N79),WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),2,IF(AND(ISNUMBER($K79),AE$5&gt;=$K79,AE$5&lt;=$L79,WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),1,""))</f>
         <v>1</v>
       </c>
       <c r="AF79" s="25" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG79" s="26" t="n">
         <v>4</v>
@@ -9602,7 +9624,7 @@
       </c>
       <c r="R80" s="29" t="n">
         <f aca="false">IF(M80="","",IF($L$1&lt;M80,0,NETWORKDAYS(M80,IF(N80="",$L$1,MIN($L$1,N80)),휴일!$A$2:$A$2)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S80" s="30" t="n">
         <f aca="false">IF(O80="","",IF(O80=0,0,Q80/O80))</f>
@@ -9648,16 +9670,16 @@
         <f aca="false">IF(AND(ISNUMBER($M80),AC$5&gt;=$M80,AC$5&lt;=IF($N80="",$L$1,$N80),WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),2,IF(AND(ISNUMBER($K80),AC$5&gt;=$K80,AC$5&lt;=$L80,WEEKDAY(AC$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AC$5)=0),1,""))</f>
         <v>2</v>
       </c>
-      <c r="AD80" s="32" t="str">
+      <c r="AD80" s="32" t="n">
         <f aca="false">IF(AND(ISNUMBER($M80),AD$5&gt;=$M80,AD$5&lt;=IF($N80="",$L$1,$N80),WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),2,IF(AND(ISNUMBER($K80),AD$5&gt;=$K80,AD$5&lt;=$L80,WEEKDAY(AD$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AD$5)=0),1,""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE80" s="32" t="n">
         <f aca="false">IF(AND(ISNUMBER($M80),AE$5&gt;=$M80,AE$5&lt;=IF($N80="",$L$1,$N80),WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),2,IF(AND(ISNUMBER($K80),AE$5&gt;=$K80,AE$5&lt;=$L80,WEEKDAY(AE$5,2)&lt;6,COUNTIF(휴일!$A$2:$A$2,AE$5)=0),1,""))</f>
         <v>1</v>
       </c>
       <c r="AF80" s="25" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AG80" s="26" t="n">
         <v>3</v>
@@ -9762,7 +9784,7 @@
         <v>1</v>
       </c>
       <c r="AF81" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG81" s="26"/>
       <c r="AH81" s="26"/>
@@ -9863,7 +9885,7 @@
         <v>1</v>
       </c>
       <c r="AF82" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG82" s="26"/>
       <c r="AH82" s="26"/>
@@ -9964,7 +9986,7 @@
         <v>1</v>
       </c>
       <c r="AF83" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG83" s="26"/>
       <c r="AH83" s="26"/>
@@ -10065,7 +10087,7 @@
         <v>1</v>
       </c>
       <c r="AF84" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG84" s="26"/>
       <c r="AH84" s="26"/>
@@ -10166,7 +10188,7 @@
         <v>1</v>
       </c>
       <c r="AF85" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG85" s="26"/>
       <c r="AH85" s="26"/>
@@ -10267,7 +10289,7 @@
         <v>1</v>
       </c>
       <c r="AF86" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG86" s="26"/>
       <c r="AH86" s="26"/>
@@ -10368,7 +10390,7 @@
         <v>1</v>
       </c>
       <c r="AF87" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG87" s="26"/>
       <c r="AH87" s="26"/>
@@ -10469,7 +10491,7 @@
         <v>1</v>
       </c>
       <c r="AF88" s="25" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG88" s="26"/>
       <c r="AH88" s="26"/>
